--- a/out/LSTM-Mamba1_repeat_5_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.3110100759941125</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.90780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-3.50780289896909</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_5_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3110100759941125</v>
+        <v>-0.4938931993099119</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-3.50780289896909</v>
+        <v>-1.366764736444358</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-3.50780289896909</v>
+        <v>-1.166764736444358</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.293893199309912</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.2938931993099119</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.90780289896909</v>
+        <v>-0.2938931993099119</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.2938931993099119</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.2938931993099119</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-3.50780289896909</v>
+        <v>-1.366764736444358</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-3.50780289896909</v>
+        <v>-2.239636273578804</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-3.50780289896909</v>
+        <v>-1.366764736444358</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9110100759941124</v>
+        <v>-0.293893199309912</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9110100759941124</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.5789783378245343</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.3110100759941125</v>
+        <v>0.3789783378245343</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_5_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01737055554986</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01016257889568806</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.006196474656462669</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5789783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.004065161570906639</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5789783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.003080517053604126</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.5789783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.002579350024461746</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.5789783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.002280723303556442</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5789783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.002350706607103348</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.5789783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.002702491357922554</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.5789783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.00248011015355587</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.002130651846528053</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.001881679520010948</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.001935649663209915</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.00195489265024662</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.001977613195776939</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.002025078982114792</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.002108786255121231</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.002174494788050652</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.002200627699494362</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.002273408696055412</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.002333668991923332</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.002342903986573219</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.002365598455071449</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002966815605759621</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.002952668815851212</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.002751311287283897</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.002588747069239616</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.002446824684739113</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.00227467343211174</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002177225425839424</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002204544842243195</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.002236530184745789</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.002297883853316307</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002383071929216385</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002565419301390648</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.002904655411839485</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.002888798713684082</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002636250108480453</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002713661640882492</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.002834741026163101</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.003094049170613289</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.003303002566099167</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.002733139321208</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.002865426242351532</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.001369262114167213</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0001589506864547729</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4938931993099119</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0006868410855531693</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.366764736444358</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0008648056536912918</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.0009633805602788925</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.0003029126673936844</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0002266056835651398</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.000299409031867981</v>
       </c>
       <c r="JB53" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0005976725369691849</v>
       </c>
       <c r="JB54" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0007936786860227585</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0006569009274244308</v>
       </c>
       <c r="JB56" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.0006220247596502304</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.000476812943816185</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.0001299884170293808</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.166764736444358</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>5.759298801422119e-06</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.293893199309912</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>4.071742296218872e-05</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5789783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.0002473555505275726</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5789783378245343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.0001626014709472656</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2938931993099119</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-2.763606607913971e-05</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2938931993099119</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>7.818266749382019e-05</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.2938931993099119</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.0003214702010154724</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5789783378245343</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.0005951542407274246</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5789783378245343</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0003114547580480576</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2938931993099119</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0002075489610433578</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.366764736444358</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0005504060536623001</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.0006470885127782822</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.0005545150488615036</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.0004692543298006058</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.239636273578804</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.0002395994961261749</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.239636273578804</v>
+        <v>0.16</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-6.929785013198853e-05</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.366764736444358</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>8.415430784225464e-06</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.293893199309912</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.000124489888548851</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.0002942569553852081</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.5789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.0004341695457696915</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.0005413200706243515</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.5789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.0006676502525806427</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.5789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.0007694084197282791</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.0009003467857837677</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.0008949413895606995</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0008689779788255692</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.5789783378245343</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0007975064218044281</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0007164850831031799</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0007935035973787308</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.0008553601801395416</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.001045087352395058</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.0008880607783794403</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.0007258318364620209</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.0007012095302343369</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.000608125701546669</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.16</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.0005593299865722656</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.16</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.0005897227674722672</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.0008290410041809082</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.0009229481220245361</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.0009929966181516647</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.001050135120749474</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.001198718324303627</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.001208789646625519</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.001293715089559555</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.001405533403158188</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.00144549272954464</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.001514460891485214</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.001575225964188576</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.001609325408935547</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.001656224951148033</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.001732949167490005</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.001772612333297729</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.00189674086868763</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.001955727115273476</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.002039816230535507</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.00203322060406208</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.002058690413832664</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.002487856894731522</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.002649644389748573</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.003235567361116409</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.002841334789991379</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.002660125494003296</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.3789783378245343</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.002085773274302483</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.16</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.001617530360817909</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.001500723883509636</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.001396756619215012</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.65</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.001701809465885162</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.3789783378245343</v>
+        <v>-0.72</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_5_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.01737055554986</v>
+        <v>0.01737054437398911</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.3</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.01016257889568806</v>
+        <v>0.01016256399452686</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.3</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.006196474656462669</v>
+        <v>0.006196444854140282</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.3</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.004065161570906639</v>
+        <v>0.004065139219164848</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.3</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.003080517053604126</v>
+        <v>0.003080461174249649</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.3</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.002579350024461746</v>
+        <v>0.002579379826784134</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.3</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.002280723303556442</v>
+        <v>0.002280764281749725</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.3</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.002350706607103348</v>
+        <v>0.002350695431232452</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.3</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.002702491357922554</v>
+        <v>0.002702463418245316</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.3</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.00248011015355587</v>
+        <v>0.002480072900652885</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.3</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.002130651846528053</v>
+        <v>0.002130748704075813</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.3</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.001881679520010948</v>
+        <v>0.001881783828139305</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.3</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.001935649663209915</v>
+        <v>0.001935724169015884</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.4399999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.00195489265024662</v>
+        <v>0.001954913139343262</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.5799999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.001977613195776939</v>
+        <v>0.001977486535906792</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.7199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.002025078982114792</v>
+        <v>0.002025006338953972</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.8599999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.002108786255121231</v>
+        <v>0.002108756452798843</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.002174494788050652</v>
+        <v>0.002174440771341324</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.9999999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.002200627699494362</v>
+        <v>0.002200629562139511</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.002273408696055412</v>
+        <v>0.002273393794894218</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.002333668991923332</v>
+        <v>0.002333711832761765</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.9999999999999998</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.002342903986573219</v>
+        <v>0.00234292633831501</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.002365598455071449</v>
+        <v>0.002365654334425926</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.002966815605759621</v>
+        <v>0.002966854721307755</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.002952668815851212</v>
+        <v>0.002952724695205688</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.002751311287283897</v>
+        <v>0.002751301974058151</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.002588747069239616</v>
+        <v>0.002588730305433273</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.002446824684739113</v>
+        <v>0.002446763217449188</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.00227467343211174</v>
+        <v>0.002274569123983383</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.9999999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.002177225425839424</v>
+        <v>0.002177121117711067</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.9999999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.002204544842243195</v>
+        <v>0.002204511314630508</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.9999999999999998</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.002236530184745789</v>
+        <v>0.002236468717455864</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.002297883853316307</v>
+        <v>0.002297839149832726</v>
       </c>
       <c r="JB34" t="n">
         <v>0.02000000000000007</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.002383071929216385</v>
+        <v>0.002383099868893623</v>
       </c>
       <c r="JB35" t="n">
         <v>0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.002565419301390648</v>
+        <v>0.002565409988164902</v>
       </c>
       <c r="JB36" t="n">
         <v>0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.002904655411839485</v>
+        <v>0.002904675900936127</v>
       </c>
       <c r="JB37" t="n">
         <v>0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.002888798713684082</v>
+        <v>0.002888811752200127</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.002636250108480453</v>
+        <v>0.00263633020222187</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.002713661640882492</v>
+        <v>0.002713615074753761</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.002834741026163101</v>
+        <v>0.002834677696228027</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.003094049170613289</v>
+        <v>0.00309392437338829</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.003303002566099167</v>
+        <v>0.003302840515971184</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.002733139321208</v>
+        <v>0.002733016386628151</v>
       </c>
       <c r="JB44" t="n">
         <v>0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.002865426242351532</v>
+        <v>0.002865346148610115</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.16</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.001369262114167213</v>
+        <v>0.00136890634894371</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.0001589506864547729</v>
+        <v>0.0001586694270372391</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.0006868410855531693</v>
+        <v>-0.0006870292127132416</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.0008648056536912918</v>
+        <v>-0.0008650384843349457</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.0009633805602788925</v>
+        <v>-0.0009635649621486664</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.0003029126673936844</v>
+        <v>-0.0003030877560377121</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.0002266056835651398</v>
+        <v>-0.0002267379313707352</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.000299409031867981</v>
+        <v>-0.000299554318189621</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.0005976725369691849</v>
+        <v>-0.000597730278968811</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.0007936786860227585</v>
+        <v>-0.0007938109338283539</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.0006569009274244308</v>
+        <v>-0.0006570033729076385</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.0006220247596502304</v>
+        <v>-0.0006221234798431396</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.000476812943816185</v>
+        <v>-0.0004768893122673035</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.0001299884170293808</v>
+        <v>-0.0001300424337387085</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>5.759298801422119e-06</v>
+        <v>5.718320608139038e-06</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>4.071742296218872e-05</v>
+        <v>4.063360393047333e-05</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.0002473555505275726</v>
+        <v>0.0002472531050443649</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.0001626014709472656</v>
+        <v>0.0001625232398509979</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-2.763606607913971e-05</v>
+        <v>-2.769194543361664e-05</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>7.818266749382019e-05</v>
+        <v>7.809698581695557e-05</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.2599999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.0003214702010154724</v>
+        <v>0.0003213845193386078</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.2599999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.0005951542407274246</v>
+        <v>0.0005950890481472015</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.2599999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.0003114547580480576</v>
+        <v>0.0003114808350801468</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.2599999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.0002075489610433578</v>
+        <v>-0.0002075862139463425</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.2599999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.0005504060536623001</v>
+        <v>-0.0005504190921783447</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.3999999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.0006470885127782822</v>
+        <v>-0.000647127628326416</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.0005545150488615036</v>
+        <v>-0.000554598867893219</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.0004692543298006058</v>
+        <v>-0.0004693344235420227</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.7199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.0002395994961261749</v>
+        <v>-0.0002396386116743088</v>
       </c>
       <c r="JB74" t="n">
         <v>0.16</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-6.929785013198853e-05</v>
+        <v>-6.933137774467468e-05</v>
       </c>
       <c r="JB75" t="n">
         <v>0.4399999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>8.415430784225464e-06</v>
+        <v>8.393079042434692e-06</v>
       </c>
       <c r="JB76" t="n">
         <v>0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.000124489888548851</v>
+        <v>0.0001245066523551941</v>
       </c>
       <c r="JB77" t="n">
         <v>0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.0002942569553852081</v>
+        <v>0.0002942383289337158</v>
       </c>
       <c r="JB78" t="n">
         <v>0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.0004341695457696915</v>
+        <v>0.0004341471940279007</v>
       </c>
       <c r="JB79" t="n">
         <v>0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.0005413200706243515</v>
+        <v>0.0005413051694631577</v>
       </c>
       <c r="JB80" t="n">
         <v>0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.0006676502525806427</v>
+        <v>0.0006676744669675827</v>
       </c>
       <c r="JB81" t="n">
         <v>0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.0007694084197282791</v>
+        <v>0.0007693823426961899</v>
       </c>
       <c r="JB82" t="n">
         <v>0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.0009003467857837677</v>
+        <v>0.0009002909064292908</v>
       </c>
       <c r="JB83" t="n">
         <v>0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.0008949413895606995</v>
+        <v>0.0008949525654315948</v>
       </c>
       <c r="JB84" t="n">
         <v>0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.0008689779788255692</v>
+        <v>0.0008689705282449722</v>
       </c>
       <c r="JB85" t="n">
         <v>0.2599999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.0007975064218044281</v>
+        <v>0.000797489657998085</v>
       </c>
       <c r="JB86" t="n">
         <v>0.1199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.0007164850831031799</v>
+        <v>0.0007164515554904938</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.02000000000000007</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.0007935035973787308</v>
+        <v>0.0007934588938951492</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.02000000000000007</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.0008553601801395416</v>
+        <v>0.0008552949875593185</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.02000000000000007</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.001045087352395058</v>
+        <v>0.001045022159814835</v>
       </c>
       <c r="JB90" t="n">
         <v>0.1199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.0008880607783794403</v>
+        <v>0.0008880086243152618</v>
       </c>
       <c r="JB91" t="n">
         <v>0.1199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.0007258318364620209</v>
+        <v>0.000725792720913887</v>
       </c>
       <c r="JB92" t="n">
         <v>0.1199999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.0007012095302343369</v>
+        <v>0.0007011778652667999</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.02000000000000007</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.000608125701546669</v>
+        <v>0.0006080921739339828</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.16</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.0005593299865722656</v>
+        <v>0.0005593448877334595</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.16</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.0005897227674722672</v>
+        <v>0.000589713454246521</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.02000000000000007</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.0008290410041809082</v>
+        <v>0.0008290465921163559</v>
       </c>
       <c r="JB97" t="n">
         <v>0.1199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.0009229481220245361</v>
+        <v>0.0009229220449924469</v>
       </c>
       <c r="JB98" t="n">
         <v>0.8599999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.0009929966181516647</v>
+        <v>0.0009930431842803955</v>
       </c>
       <c r="JB99" t="n">
         <v>0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.001050135120749474</v>
+        <v>0.001050161197781563</v>
       </c>
       <c r="JB100" t="n">
         <v>0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.001198718324303627</v>
+        <v>0.001198716461658478</v>
       </c>
       <c r="JB101" t="n">
         <v>0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.001208789646625519</v>
+        <v>0.001208873465657234</v>
       </c>
       <c r="JB102" t="n">
         <v>0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.001293715089559555</v>
+        <v>0.001293741166591644</v>
       </c>
       <c r="JB103" t="n">
         <v>0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.001405533403158188</v>
+        <v>0.001405563205480576</v>
       </c>
       <c r="JB104" t="n">
         <v>0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.00144549272954464</v>
+        <v>0.001445433124899864</v>
       </c>
       <c r="JB105" t="n">
         <v>0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.001514460891485214</v>
+        <v>0.001514405012130737</v>
       </c>
       <c r="JB106" t="n">
         <v>0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.001575225964188576</v>
+        <v>0.001575171947479248</v>
       </c>
       <c r="JB107" t="n">
         <v>0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.001609325408935547</v>
+        <v>0.001609288156032562</v>
       </c>
       <c r="JB108" t="n">
         <v>0.3999999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.001656224951148033</v>
+        <v>0.001656195148825645</v>
       </c>
       <c r="JB109" t="n">
         <v>0.3999999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.001732949167490005</v>
+        <v>0.001732895150780678</v>
       </c>
       <c r="JB110" t="n">
         <v>0.3999999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.001772612333297729</v>
+        <v>0.001772608608007431</v>
       </c>
       <c r="JB111" t="n">
         <v>0.3999999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.00189674086868763</v>
+        <v>0.001896735280752182</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3999999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.001955727115273476</v>
+        <v>0.001955782994627953</v>
       </c>
       <c r="JB113" t="n">
         <v>0.3999999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.002039816230535507</v>
+        <v>0.002039803192019463</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3999999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.00203322060406208</v>
+        <v>0.002033200114965439</v>
       </c>
       <c r="JB115" t="n">
         <v>0.3999999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.002058690413832664</v>
+        <v>0.002058666199445724</v>
       </c>
       <c r="JB116" t="n">
         <v>0.3999999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.002487856894731522</v>
+        <v>0.002487823367118835</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3999999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.002649644389748573</v>
+        <v>0.002649599686264992</v>
       </c>
       <c r="JB118" t="n">
         <v>0.3999999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.003235567361116409</v>
+        <v>0.003235504031181335</v>
       </c>
       <c r="JB119" t="n">
         <v>0.3999999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.002841334789991379</v>
+        <v>0.00284133292734623</v>
       </c>
       <c r="JB120" t="n">
         <v>0.2599999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.002660125494003296</v>
+        <v>0.002660106867551804</v>
       </c>
       <c r="JB121" t="n">
         <v>0.1199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.002085773274302483</v>
+        <v>0.002085741609334946</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.16</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.001617530360817909</v>
+        <v>0.001617498695850372</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.001500723883509636</v>
+        <v>0.001500757411122322</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.5799999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.001396756619215012</v>
+        <v>0.001396793872117996</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.65</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.001701809465885162</v>
+        <v>0.001701831817626953</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.72</v>
